--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="462">
   <si>
     <t/>
   </si>
@@ -859,6 +859,12 @@
     <t>TEREA RIVIERA PR 20S</t>
   </si>
   <si>
+    <t>20143996</t>
+  </si>
+  <si>
+    <t>TEREA STRAW PEARL20S</t>
+  </si>
+  <si>
     <t>20128089</t>
   </si>
   <si>
@@ -871,18 +877,18 @@
     <t>TEREA AUBURN ED 20'S</t>
   </si>
   <si>
-    <t>20134382</t>
-  </si>
-  <si>
-    <t>TEREA BERRNE ED 20'S</t>
-  </si>
-  <si>
     <t>20138206</t>
   </si>
   <si>
     <t>TEREA BLACK RUBY20S</t>
   </si>
   <si>
+    <t>20143994</t>
+  </si>
+  <si>
+    <t>TEREA PAS FRT PRL20S</t>
+  </si>
+  <si>
     <t>20136323</t>
   </si>
   <si>
@@ -1315,12 +1321,6 @@
     <t>ESSE CHG DBL PINPL20</t>
   </si>
   <si>
-    <t>20038143</t>
-  </si>
-  <si>
-    <t>GG SURYA EXCLSIVE16S</t>
-  </si>
-  <si>
     <t>10010077</t>
   </si>
   <si>
@@ -1345,12 +1345,6 @@
     <t>G/G  SGNTURE 12</t>
   </si>
   <si>
-    <t>20098634</t>
-  </si>
-  <si>
-    <t>GG KRTEK PATRA 12'S</t>
-  </si>
-  <si>
     <t>20069791</t>
   </si>
   <si>
@@ -1379,12 +1373,6 @@
   </si>
   <si>
     <t>GG KRETEK DELUXE12'S</t>
-  </si>
-  <si>
-    <t>20062962</t>
-  </si>
-  <si>
-    <t>GG KRTK DELUXE 16S</t>
   </si>
   <si>
     <t>20058026</t>
@@ -1801,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4425,7 +4413,7 @@
         <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4505,7 +4493,7 @@
         <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4608,7 +4596,7 @@
         <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4645,10 +4633,10 @@
         <v>33</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4708,7 +4696,7 @@
         <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4768,7 +4756,7 @@
         <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4888,7 +4876,7 @@
         <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4908,7 +4896,7 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4928,7 +4916,7 @@
         <v>18</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4965,7 +4953,7 @@
         <v>33</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>9</v>
@@ -5048,7 +5036,7 @@
         <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5125,7 +5113,7 @@
         <v>33</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5142,10 +5130,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5165,7 +5153,7 @@
         <v>36</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5185,7 +5173,7 @@
         <v>36</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5205,7 +5193,7 @@
         <v>36</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5225,7 +5213,7 @@
         <v>36</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5245,7 +5233,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5265,7 +5253,7 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5285,7 +5273,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5305,7 +5293,7 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5325,7 +5313,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5345,10 +5333,10 @@
         <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5365,10 +5353,10 @@
         <v>36</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5385,10 +5373,10 @@
         <v>36</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5405,10 +5393,10 @@
         <v>36</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5422,10 +5410,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5445,7 +5433,7 @@
         <v>39</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5465,7 +5453,7 @@
         <v>39</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5485,7 +5473,7 @@
         <v>39</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5505,7 +5493,7 @@
         <v>39</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5525,7 +5513,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5545,7 +5533,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5565,7 +5553,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5585,7 +5573,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5605,7 +5593,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5625,7 +5613,7 @@
         <v>39</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5645,7 +5633,7 @@
         <v>39</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5662,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5685,7 +5673,7 @@
         <v>42</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5705,7 +5693,7 @@
         <v>42</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5725,7 +5713,7 @@
         <v>42</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5745,10 +5733,10 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5765,7 +5753,7 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>9</v>
@@ -5785,7 +5773,7 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>9</v>
@@ -5805,10 +5793,10 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5825,7 +5813,7 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5845,7 +5833,7 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>5</v>
@@ -5865,7 +5853,7 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>5</v>
@@ -5885,7 +5873,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5905,7 +5893,7 @@
         <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5925,7 +5913,7 @@
         <v>42</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5942,10 +5930,10 @@
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E207" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -6045,7 +6033,7 @@
         <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6062,10 +6050,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6085,7 +6073,7 @@
         <v>93</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6105,7 +6093,7 @@
         <v>93</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6125,7 +6113,7 @@
         <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6145,7 +6133,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6165,7 +6153,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6185,7 +6173,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6205,49 +6193,9 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E221" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F222" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="467">
   <si>
     <t/>
   </si>
@@ -790,27 +790,24 @@
     <t>IDM LGHT CRCKT ELKTR</t>
   </si>
   <si>
+    <t>20142352</t>
+  </si>
+  <si>
+    <t>IDM UTILITY LIGHTER</t>
+  </si>
+  <si>
     <t>16</t>
   </si>
   <si>
-    <t>20142352</t>
-  </si>
-  <si>
-    <t>IDM UTILITY LIGHTER</t>
+    <t>20142409</t>
+  </si>
+  <si>
+    <t>IDM LIGHTER EL M2000</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>20142409</t>
-  </si>
-  <si>
-    <t>IDM LIGHTER EL M2000</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>20128084</t>
   </si>
   <si>
@@ -1163,6 +1160,24 @@
   </si>
   <si>
     <t>CAMEL KRETK KLSK 10S</t>
+  </si>
+  <si>
+    <t>20143811</t>
+  </si>
+  <si>
+    <t>JUARA INTNS PUCUK12S</t>
+  </si>
+  <si>
+    <t>20143812</t>
+  </si>
+  <si>
+    <t>JUARA INTNS MRKSA12S</t>
+  </si>
+  <si>
+    <t>20143813</t>
+  </si>
+  <si>
+    <t>JUARA INTNS J/JBU12S</t>
   </si>
   <si>
     <t>20130571</t>
@@ -1789,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F220"/>
+  <dimension ref="A1:F223"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4053,7 +4068,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4073,7 +4088,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4093,7 +4108,7 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4113,7 +4128,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4133,7 +4148,7 @@
         <v>30</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4153,7 +4168,7 @@
         <v>30</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4173,7 +4188,7 @@
         <v>30</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>49</v>
@@ -4193,7 +4208,7 @@
         <v>30</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>259</v>
+        <v>93</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4201,10 +4216,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4213,7 +4228,7 @@
         <v>30</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>9</v>
@@ -4221,10 +4236,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4233,7 +4248,7 @@
         <v>30</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>9</v>
@@ -4241,10 +4256,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4261,10 +4276,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>269</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4281,10 +4296,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>271</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4301,10 +4316,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4321,10 +4336,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>275</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4341,10 +4356,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4361,10 +4376,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4381,10 +4396,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4401,10 +4416,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4421,10 +4436,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4441,10 +4456,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4461,10 +4476,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4481,10 +4496,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4501,10 +4516,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4521,10 +4536,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4541,10 +4556,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4561,10 +4576,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4581,10 +4596,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4601,10 +4616,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4621,10 +4636,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4641,10 +4656,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4661,10 +4676,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4681,10 +4696,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4701,10 +4716,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4721,10 +4736,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4741,10 +4756,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4761,10 +4776,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4781,10 +4796,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4801,10 +4816,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4821,10 +4836,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4841,10 +4856,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4861,10 +4876,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4881,10 +4896,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>331</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4901,10 +4916,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4921,10 +4936,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4941,10 +4956,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4961,10 +4976,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>339</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -4981,10 +4996,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -5001,10 +5016,10 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -5021,10 +5036,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -5041,10 +5056,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>347</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -5061,10 +5076,10 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>349</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -5081,10 +5096,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -5101,10 +5116,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -5121,10 +5136,10 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -5141,10 +5156,10 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>357</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
@@ -5161,10 +5176,10 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
@@ -5181,10 +5196,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5201,10 +5216,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5221,10 +5236,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5241,10 +5256,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5261,10 +5276,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5281,10 +5296,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5301,10 +5316,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5321,10 +5336,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5341,10 +5356,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5361,10 +5376,10 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5381,10 +5396,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>381</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5401,10 +5416,10 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>382</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5421,10 +5436,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5441,10 +5456,10 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5461,10 +5476,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>389</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5481,10 +5496,10 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
@@ -5501,10 +5516,10 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
@@ -5521,10 +5536,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>395</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
@@ -5541,10 +5556,10 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
@@ -5561,10 +5576,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
@@ -5581,10 +5596,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
@@ -5601,10 +5616,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>403</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -5621,10 +5636,10 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>405</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
@@ -5641,10 +5656,10 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
@@ -5661,19 +5676,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5681,19 +5696,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5701,19 +5716,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5721,10 +5736,10 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
@@ -5733,7 +5748,7 @@
         <v>42</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5741,10 +5756,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
@@ -5753,18 +5768,18 @@
         <v>42</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="B199" s="1" t="s">
-        <v>419</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
@@ -5773,18 +5788,18 @@
         <v>42</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
@@ -5793,18 +5808,18 @@
         <v>42</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
@@ -5813,18 +5828,18 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
@@ -5833,18 +5848,18 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
@@ -5853,18 +5868,18 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>429</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
@@ -5873,7 +5888,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5881,10 +5896,10 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
@@ -5893,7 +5908,7 @@
         <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -5901,10 +5916,10 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
@@ -5913,7 +5928,7 @@
         <v>42</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -5921,10 +5936,10 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
@@ -5933,7 +5948,7 @@
         <v>42</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>5</v>
@@ -5941,19 +5956,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>437</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5961,19 +5976,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5981,19 +5996,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E210" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E210" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6001,10 +6016,10 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
@@ -6013,7 +6028,7 @@
         <v>90</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6021,10 +6036,10 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
@@ -6033,7 +6048,7 @@
         <v>90</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6041,19 +6056,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>447</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6061,19 +6076,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>449</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6081,19 +6096,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>451</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6101,10 +6116,10 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
@@ -6113,7 +6128,7 @@
         <v>93</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6121,10 +6136,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
@@ -6133,7 +6148,7 @@
         <v>93</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6141,10 +6156,10 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
@@ -6153,7 +6168,7 @@
         <v>93</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6161,10 +6176,10 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
@@ -6173,7 +6188,7 @@
         <v>93</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6181,10 +6196,10 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B220" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
@@ -6193,9 +6208,69 @@
         <v>93</v>
       </c>
       <c r="E220" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E223" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F220" s="1" t="s">
+      <c r="F223" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/DJM02N.xlsx
+++ b/DJM02N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="483">
   <si>
     <t/>
   </si>
@@ -199,6 +199,12 @@
     <t>MRLBORO KRT BIRU 12S</t>
   </si>
   <si>
+    <t>20143809</t>
+  </si>
+  <si>
+    <t>DJISAMSU MGNM MSTR12</t>
+  </si>
+  <si>
     <t>10010094</t>
   </si>
   <si>
@@ -700,6 +706,684 @@
     <t>LA FILTER LIGHT 16'S</t>
   </si>
   <si>
+    <t>20144453</t>
+  </si>
+  <si>
+    <t>DJRM BLCK MCHA SRO16</t>
+  </si>
+  <si>
+    <t>20144454</t>
+  </si>
+  <si>
+    <t>DJRM BLCK MCHA KRO16</t>
+  </si>
+  <si>
+    <t>20137797</t>
+  </si>
+  <si>
+    <t>DPLOMAT EVO MGO 16'S</t>
+  </si>
+  <si>
+    <t>20137798</t>
+  </si>
+  <si>
+    <t>DIPLOMAT EVO BERY16S</t>
+  </si>
+  <si>
+    <t>20139165</t>
+  </si>
+  <si>
+    <t>DIPLOMAT EVO LYCH16S</t>
+  </si>
+  <si>
+    <t>20102167</t>
+  </si>
+  <si>
+    <t>DIPLOMAT EVO16'S</t>
+  </si>
+  <si>
+    <t>20143212</t>
+  </si>
+  <si>
+    <t>3VO CLICK MATCHA16S</t>
+  </si>
+  <si>
+    <t>20143989</t>
+  </si>
+  <si>
+    <t>3VO SLEK MLN APLE20S</t>
+  </si>
+  <si>
+    <t>20143988</t>
+  </si>
+  <si>
+    <t>3VO SLEK MGO APLE20S</t>
+  </si>
+  <si>
+    <t>20141244</t>
+  </si>
+  <si>
+    <t>WISMILAK SLIM LYC16S</t>
+  </si>
+  <si>
+    <t>20101053</t>
+  </si>
+  <si>
+    <t>JAZY BOLD MILD 20'S</t>
+  </si>
+  <si>
+    <t>20136523</t>
+  </si>
+  <si>
+    <t>JAZY RK POPPIN16'S</t>
+  </si>
+  <si>
+    <t>20131551</t>
+  </si>
+  <si>
+    <t>JAZY KRETEK 12'S</t>
+  </si>
+  <si>
+    <t>20142823</t>
+  </si>
+  <si>
+    <t>JAZY MAX FILTER 12'S</t>
+  </si>
+  <si>
+    <t>20095233</t>
+  </si>
+  <si>
+    <t>IDM LGHT CRCKET SLID</t>
+  </si>
+  <si>
+    <t>20123763</t>
+  </si>
+  <si>
+    <t>IDM LGHT TOKAI MOTIF</t>
+  </si>
+  <si>
+    <t>20070579</t>
+  </si>
+  <si>
+    <t>IDM LGHT CRCKT ELKTR</t>
+  </si>
+  <si>
+    <t>20142352</t>
+  </si>
+  <si>
+    <t>IDM UTILITY LIGHTER</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20142409</t>
+  </si>
+  <si>
+    <t>IDM LIGHTER EL M2000</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20128084</t>
+  </si>
+  <si>
+    <t>TEREA BLUE 20'S</t>
+  </si>
+  <si>
+    <t>20128085</t>
+  </si>
+  <si>
+    <t>TEREA BLCK GRN 20'S</t>
+  </si>
+  <si>
+    <t>20128086</t>
+  </si>
+  <si>
+    <t>TEREA SIENNA 20'S</t>
+  </si>
+  <si>
+    <t>20135433</t>
+  </si>
+  <si>
+    <t>TEREA SUN PEARL 20'S</t>
+  </si>
+  <si>
+    <t>20135434</t>
+  </si>
+  <si>
+    <t>TEREA OASIS PRL 20'S</t>
+  </si>
+  <si>
+    <t>20132739</t>
+  </si>
+  <si>
+    <t>TEREA GOLDEN ED 20'S</t>
+  </si>
+  <si>
+    <t>20134380</t>
+  </si>
+  <si>
+    <t>TEREA MULINT ED 20'S</t>
+  </si>
+  <si>
+    <t>20140875</t>
+  </si>
+  <si>
+    <t>TEREA RIVIERA PR 20S</t>
+  </si>
+  <si>
+    <t>20143996</t>
+  </si>
+  <si>
+    <t>TEREA STRAW PEARL20S</t>
+  </si>
+  <si>
+    <t>20128089</t>
+  </si>
+  <si>
+    <t>TEREA YUGEN 20'S</t>
+  </si>
+  <si>
+    <t>20134381</t>
+  </si>
+  <si>
+    <t>TEREA AUBURN ED 20'S</t>
+  </si>
+  <si>
+    <t>20138206</t>
+  </si>
+  <si>
+    <t>TEREA BLACK RUBY20S</t>
+  </si>
+  <si>
+    <t>20143994</t>
+  </si>
+  <si>
+    <t>TEREA PAS FRT PRL20S</t>
+  </si>
+  <si>
+    <t>20136323</t>
+  </si>
+  <si>
+    <t>BLENDS WARM.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20136324</t>
+  </si>
+  <si>
+    <t>BLENDS PRPL.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20136326</t>
+  </si>
+  <si>
+    <t>BLENDS SMMR.EDT 20'S</t>
+  </si>
+  <si>
+    <t>20139349</t>
+  </si>
+  <si>
+    <t>TEREA PERINT PRL 20S</t>
+  </si>
+  <si>
+    <t>20140879</t>
+  </si>
+  <si>
+    <t>BLENDS TROPICAL 20'S</t>
+  </si>
+  <si>
+    <t>20143379</t>
+  </si>
+  <si>
+    <t>BLENDS  WTRMLN MIX20</t>
+  </si>
+  <si>
+    <t>20143382</t>
+  </si>
+  <si>
+    <t>BLENDS PASS FRTMIX20</t>
+  </si>
+  <si>
+    <t>20135189</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 STRWBRY</t>
+  </si>
+  <si>
+    <t>20135190</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 RED.MLN</t>
+  </si>
+  <si>
+    <t>20135191</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 MANGO</t>
+  </si>
+  <si>
+    <t>20137965</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 S.APPLE</t>
+  </si>
+  <si>
+    <t>20137967</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 BLUEBRY</t>
+  </si>
+  <si>
+    <t>20137968</t>
+  </si>
+  <si>
+    <t>VEEV ONE1000 GRAPE</t>
+  </si>
+  <si>
+    <t>20139616</t>
+  </si>
+  <si>
+    <t>VEEV ONE 1000 CHERRY</t>
+  </si>
+  <si>
+    <t>20139759</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 MANGO</t>
+  </si>
+  <si>
+    <t>20139760</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 RED MLN</t>
+  </si>
+  <si>
+    <t>20139761</t>
+  </si>
+  <si>
+    <t>VEEV ONE 500 STRW CL</t>
+  </si>
+  <si>
+    <t>20140265</t>
+  </si>
+  <si>
+    <t>VEEV ONE 1000 LT.TEA</t>
+  </si>
+  <si>
+    <t>20140267</t>
+  </si>
+  <si>
+    <t>VEEV ONE 1000 LM.TEA</t>
+  </si>
+  <si>
+    <t>20142476</t>
+  </si>
+  <si>
+    <t>VEEVA PODS GRAPE</t>
+  </si>
+  <si>
+    <t>20142671</t>
+  </si>
+  <si>
+    <t>VEEVA ULTRA CHERRY</t>
+  </si>
+  <si>
+    <t>20143055</t>
+  </si>
+  <si>
+    <t>VEEVA POD BLUBERY500</t>
+  </si>
+  <si>
+    <t>20143072</t>
+  </si>
+  <si>
+    <t>VEEVA SOUR APPLE500</t>
+  </si>
+  <si>
+    <t>20137962</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA MNGO</t>
+  </si>
+  <si>
+    <t>20137963</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA GRPE</t>
+  </si>
+  <si>
+    <t>20137964</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULT RED.MLN</t>
+  </si>
+  <si>
+    <t>20138345</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULT SOURPLE</t>
+  </si>
+  <si>
+    <t>20138659</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA STRWB</t>
+  </si>
+  <si>
+    <t>20138763</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTR STR CL</t>
+  </si>
+  <si>
+    <t>20139526</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA RSPBR</t>
+  </si>
+  <si>
+    <t>20140252</t>
+  </si>
+  <si>
+    <t>VEEV NOW ULTRA LMN.T</t>
+  </si>
+  <si>
+    <t>20135188</t>
+  </si>
+  <si>
+    <t>VEEV DVCE KIT SP.GRY</t>
+  </si>
+  <si>
+    <t>20117925</t>
+  </si>
+  <si>
+    <t>CAMEL MILD BLUE 16'S</t>
+  </si>
+  <si>
+    <t>20130840</t>
+  </si>
+  <si>
+    <t>CAMEL WHITE NEW 20'S</t>
+  </si>
+  <si>
+    <t>20046794</t>
+  </si>
+  <si>
+    <t>CAMEL WHITE 20'S</t>
+  </si>
+  <si>
+    <t>20115758</t>
+  </si>
+  <si>
+    <t>CAMEL YLOW NEW 20'S</t>
+  </si>
+  <si>
+    <t>20096502</t>
+  </si>
+  <si>
+    <t>CAMEL YELLOW 20'S</t>
+  </si>
+  <si>
+    <t>20060300</t>
+  </si>
+  <si>
+    <t>CAMEL ACT.P MINT 20S</t>
+  </si>
+  <si>
+    <t>20128470</t>
+  </si>
+  <si>
+    <t>CAMEL OPT PURPLE 16S</t>
+  </si>
+  <si>
+    <t>20106190</t>
+  </si>
+  <si>
+    <t>CAMEL OPT PURPLE 12S</t>
+  </si>
+  <si>
+    <t>20114049</t>
+  </si>
+  <si>
+    <t>CAMEL OPT YELLOW 12S</t>
+  </si>
+  <si>
+    <t>20133512</t>
+  </si>
+  <si>
+    <t>CAMEL ACTV MNTHL 20S</t>
+  </si>
+  <si>
+    <t>20138432</t>
+  </si>
+  <si>
+    <t>CAMEL ICE RED 16S</t>
+  </si>
+  <si>
+    <t>20137297</t>
+  </si>
+  <si>
+    <t>CAMEL  KRETEK12'S</t>
+  </si>
+  <si>
+    <t>20142259</t>
+  </si>
+  <si>
+    <t>CAMEL ICE LIME 16S</t>
+  </si>
+  <si>
+    <t>20143273</t>
+  </si>
+  <si>
+    <t>CAMEL KRETK KLSK 10S</t>
+  </si>
+  <si>
+    <t>20143811</t>
+  </si>
+  <si>
+    <t>JUARA INTNS PUCUK12S</t>
+  </si>
+  <si>
+    <t>20143812</t>
+  </si>
+  <si>
+    <t>JUARA INTNS MRKSA12S</t>
+  </si>
+  <si>
+    <t>20143813</t>
+  </si>
+  <si>
+    <t>JUARA INTNS J/JBU12S</t>
+  </si>
+  <si>
+    <t>20130571</t>
+  </si>
+  <si>
+    <t>WIN FILTER CLICK20'S</t>
+  </si>
+  <si>
+    <t>20119629</t>
+  </si>
+  <si>
+    <t>WIN FILTER 20'S</t>
+  </si>
+  <si>
+    <t>20136050</t>
+  </si>
+  <si>
+    <t>WIN KRETEK BERRY 12S</t>
+  </si>
+  <si>
+    <t>20108797</t>
+  </si>
+  <si>
+    <t>WIN BOLD 20'S</t>
+  </si>
+  <si>
+    <t>20135739</t>
+  </si>
+  <si>
+    <t>CLIMAX ICY BKS 20'S</t>
+  </si>
+  <si>
+    <t>20135737</t>
+  </si>
+  <si>
+    <t>CLIMAX MANGO BKS20'S</t>
+  </si>
+  <si>
+    <t>20135736</t>
+  </si>
+  <si>
+    <t>CLIMAX MIX BKS 20'S</t>
+  </si>
+  <si>
+    <t>20112661</t>
+  </si>
+  <si>
+    <t>ESSE PUNCH POP 16'S</t>
+  </si>
+  <si>
+    <t>20070447</t>
+  </si>
+  <si>
+    <t>ESSE BERRY POP 16'S</t>
+  </si>
+  <si>
+    <t>20093678</t>
+  </si>
+  <si>
+    <t>ESSE BLUE CHNGE 20'S</t>
+  </si>
+  <si>
+    <t>20010960</t>
+  </si>
+  <si>
+    <t>ESSE FILTER BLUE 20S</t>
+  </si>
+  <si>
+    <t>20126307</t>
+  </si>
+  <si>
+    <t>ESSE DOUBLE POP 16'S</t>
+  </si>
+  <si>
+    <t>20138128</t>
+  </si>
+  <si>
+    <t>JUARA  APEL 12S</t>
+  </si>
+  <si>
+    <t>20095302</t>
+  </si>
+  <si>
+    <t>JUARA  TEH 12S</t>
+  </si>
+  <si>
+    <t>20139245</t>
+  </si>
+  <si>
+    <t>JUARA KRT  BERRY 12S</t>
+  </si>
+  <si>
+    <t>20130785</t>
+  </si>
+  <si>
+    <t>JUARA  JAMBU12S</t>
+  </si>
+  <si>
+    <t>20141660</t>
+  </si>
+  <si>
+    <t>JUARA KRT PISANG 12S</t>
+  </si>
+  <si>
+    <t>20142217</t>
+  </si>
+  <si>
+    <t>JUARA KLIK GRN GRP12</t>
+  </si>
+  <si>
+    <t>20142218</t>
+  </si>
+  <si>
+    <t>JUARA KLIK BERRY 12S</t>
+  </si>
+  <si>
+    <t>20085760</t>
+  </si>
+  <si>
+    <t>ESSE CHANGE GRP 20'S</t>
+  </si>
+  <si>
+    <t>20112781</t>
+  </si>
+  <si>
+    <t>ESSE CHNG JUICY 16'S</t>
+  </si>
+  <si>
+    <t>20094203</t>
+  </si>
+  <si>
+    <t>ESSE CHNG JUICY 20'S</t>
+  </si>
+  <si>
+    <t>20112785</t>
+  </si>
+  <si>
+    <t>ESSE CHNG APLMNT 16S</t>
+  </si>
+  <si>
+    <t>20055795</t>
+  </si>
+  <si>
+    <t>ESSE CHNG APLMNT 20S</t>
+  </si>
+  <si>
+    <t>20100795</t>
+  </si>
+  <si>
+    <t>ESSE CHNG DOUB 20'S</t>
+  </si>
+  <si>
+    <t>20143095</t>
+  </si>
+  <si>
+    <t>ESSE CHG DBL PINPL20</t>
+  </si>
+  <si>
+    <t>10010077</t>
+  </si>
+  <si>
+    <t>GG SURYA PRO 16'S</t>
+  </si>
+  <si>
+    <t>20054562</t>
+  </si>
+  <si>
+    <t>GG MILD SHIVER 16'S</t>
+  </si>
+  <si>
+    <t>20029731</t>
+  </si>
+  <si>
+    <t>GG SURYA PRO MLD16'S</t>
+  </si>
+  <si>
+    <t>20048021</t>
+  </si>
+  <si>
+    <t>G/G  SGNTURE 12</t>
+  </si>
+  <si>
+    <t>20069791</t>
+  </si>
+  <si>
+    <t>GG SIGNT MILD 16'S</t>
+  </si>
+  <si>
     <t>20136196</t>
   </si>
   <si>
@@ -712,658 +1396,16 @@
     <t>CLAS MILD FILTER 16S</t>
   </si>
   <si>
-    <t>20137797</t>
-  </si>
-  <si>
-    <t>DPLOMAT EVO MGO 16'S</t>
-  </si>
-  <si>
-    <t>20137798</t>
-  </si>
-  <si>
-    <t>DIPLOMAT EVO BERY16S</t>
-  </si>
-  <si>
-    <t>20139165</t>
-  </si>
-  <si>
-    <t>DIPLOMAT EVO LYCH16S</t>
-  </si>
-  <si>
-    <t>20102167</t>
-  </si>
-  <si>
-    <t>DIPLOMAT EVO16'S</t>
-  </si>
-  <si>
-    <t>20143212</t>
-  </si>
-  <si>
-    <t>3VO CLICK MATCHA16S</t>
-  </si>
-  <si>
-    <t>20141244</t>
-  </si>
-  <si>
-    <t>WISMILAK SLIM LYC16S</t>
-  </si>
-  <si>
-    <t>20101053</t>
-  </si>
-  <si>
-    <t>JAZY BOLD MILD 20'S</t>
-  </si>
-  <si>
-    <t>20136523</t>
-  </si>
-  <si>
-    <t>JAZY RK POPPIN16'S</t>
-  </si>
-  <si>
-    <t>20131551</t>
-  </si>
-  <si>
-    <t>JAZY KRETEK 12'S</t>
-  </si>
-  <si>
-    <t>20142823</t>
-  </si>
-  <si>
-    <t>JAZY MAX FILTER 12'S</t>
-  </si>
-  <si>
-    <t>20095233</t>
-  </si>
-  <si>
-    <t>IDM LGHT CRCKET SLID</t>
-  </si>
-  <si>
-    <t>20123763</t>
-  </si>
-  <si>
-    <t>IDM LGHT TOKAI MOTIF</t>
-  </si>
-  <si>
-    <t>20070579</t>
-  </si>
-  <si>
-    <t>IDM LGHT CRCKT ELKTR</t>
-  </si>
-  <si>
-    <t>20142352</t>
-  </si>
-  <si>
-    <t>IDM UTILITY LIGHTER</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20142409</t>
-  </si>
-  <si>
-    <t>IDM LIGHTER EL M2000</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20128084</t>
-  </si>
-  <si>
-    <t>TEREA BLUE 20'S</t>
-  </si>
-  <si>
-    <t>20128085</t>
-  </si>
-  <si>
-    <t>TEREA BLCK GRN 20'S</t>
-  </si>
-  <si>
-    <t>20128086</t>
-  </si>
-  <si>
-    <t>TEREA SIENNA 20'S</t>
-  </si>
-  <si>
-    <t>20135433</t>
-  </si>
-  <si>
-    <t>TEREA SUN PEARL 20'S</t>
-  </si>
-  <si>
-    <t>20135434</t>
-  </si>
-  <si>
-    <t>TEREA OASIS PRL 20'S</t>
-  </si>
-  <si>
-    <t>20132739</t>
-  </si>
-  <si>
-    <t>TEREA GOLDEN ED 20'S</t>
-  </si>
-  <si>
-    <t>20134380</t>
-  </si>
-  <si>
-    <t>TEREA MULINT ED 20'S</t>
-  </si>
-  <si>
-    <t>20140875</t>
-  </si>
-  <si>
-    <t>TEREA RIVIERA PR 20S</t>
-  </si>
-  <si>
-    <t>20143996</t>
-  </si>
-  <si>
-    <t>TEREA STRAW PEARL20S</t>
-  </si>
-  <si>
-    <t>20128089</t>
-  </si>
-  <si>
-    <t>TEREA YUGEN 20'S</t>
-  </si>
-  <si>
-    <t>20134381</t>
-  </si>
-  <si>
-    <t>TEREA AUBURN ED 20'S</t>
-  </si>
-  <si>
-    <t>20138206</t>
-  </si>
-  <si>
-    <t>TEREA BLACK RUBY20S</t>
-  </si>
-  <si>
-    <t>20143994</t>
-  </si>
-  <si>
-    <t>TEREA PAS FRT PRL20S</t>
-  </si>
-  <si>
-    <t>20136323</t>
-  </si>
-  <si>
-    <t>BLENDS WARM.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20136324</t>
-  </si>
-  <si>
-    <t>BLENDS PRPL.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20136326</t>
-  </si>
-  <si>
-    <t>BLENDS SMMR.EDT 20'S</t>
-  </si>
-  <si>
-    <t>20139349</t>
-  </si>
-  <si>
-    <t>TEREA PERINT PRL 20S</t>
-  </si>
-  <si>
-    <t>20140879</t>
-  </si>
-  <si>
-    <t>BLENDS TROPICAL 20'S</t>
-  </si>
-  <si>
-    <t>20143379</t>
-  </si>
-  <si>
-    <t>BLENDS  WTRMLN MIX20</t>
-  </si>
-  <si>
-    <t>20143382</t>
-  </si>
-  <si>
-    <t>BLENDS PASS FRTMIX20</t>
-  </si>
-  <si>
-    <t>20135189</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 STRWBRY</t>
-  </si>
-  <si>
-    <t>20135190</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 RED.MLN</t>
-  </si>
-  <si>
-    <t>20135191</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 MANGO</t>
-  </si>
-  <si>
-    <t>20137965</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 S.APPLE</t>
-  </si>
-  <si>
-    <t>20137967</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 BLUEBRY</t>
-  </si>
-  <si>
-    <t>20137968</t>
-  </si>
-  <si>
-    <t>VEEV ONE1000 GRAPE</t>
-  </si>
-  <si>
-    <t>20139616</t>
-  </si>
-  <si>
-    <t>VEEV ONE 1000 CHERRY</t>
-  </si>
-  <si>
-    <t>20139759</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 MANGO</t>
-  </si>
-  <si>
-    <t>20139760</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 RED MLN</t>
-  </si>
-  <si>
-    <t>20139761</t>
-  </si>
-  <si>
-    <t>VEEV ONE 500 STRW CL</t>
-  </si>
-  <si>
-    <t>20140265</t>
-  </si>
-  <si>
-    <t>VEEV ONE 1000 LT.TEA</t>
-  </si>
-  <si>
-    <t>20140267</t>
-  </si>
-  <si>
-    <t>VEEV ONE 1000 LM.TEA</t>
-  </si>
-  <si>
-    <t>20142476</t>
-  </si>
-  <si>
-    <t>VEEVA PODS GRAPE</t>
-  </si>
-  <si>
-    <t>20142671</t>
-  </si>
-  <si>
-    <t>VEEVA ULTRA CHERRY</t>
-  </si>
-  <si>
-    <t>20143055</t>
-  </si>
-  <si>
-    <t>VEEVA POD BLUBERY500</t>
-  </si>
-  <si>
-    <t>20143072</t>
-  </si>
-  <si>
-    <t>VEEVA SOUR APPLE500</t>
-  </si>
-  <si>
-    <t>20137962</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA MNGO</t>
-  </si>
-  <si>
-    <t>20137963</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA GRPE</t>
-  </si>
-  <si>
-    <t>20137964</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULT RED.MLN</t>
-  </si>
-  <si>
-    <t>20138345</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULT SOURPLE</t>
-  </si>
-  <si>
-    <t>20138659</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA STRWB</t>
-  </si>
-  <si>
-    <t>20138763</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTR STR CL</t>
-  </si>
-  <si>
-    <t>20139526</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA RSPBR</t>
-  </si>
-  <si>
-    <t>20140252</t>
-  </si>
-  <si>
-    <t>VEEV NOW ULTRA LMN.T</t>
-  </si>
-  <si>
-    <t>20135188</t>
-  </si>
-  <si>
-    <t>VEEV DVCE KIT SP.GRY</t>
-  </si>
-  <si>
-    <t>20117925</t>
-  </si>
-  <si>
-    <t>CAMEL MILD BLUE 16'S</t>
-  </si>
-  <si>
-    <t>20130840</t>
-  </si>
-  <si>
-    <t>CAMEL WHITE NEW 20'S</t>
-  </si>
-  <si>
-    <t>20046794</t>
-  </si>
-  <si>
-    <t>CAMEL WHITE 20'S</t>
-  </si>
-  <si>
-    <t>20115758</t>
-  </si>
-  <si>
-    <t>CAMEL YLOW NEW 20'S</t>
-  </si>
-  <si>
-    <t>20096502</t>
-  </si>
-  <si>
-    <t>CAMEL YELLOW 20'S</t>
-  </si>
-  <si>
-    <t>20060300</t>
-  </si>
-  <si>
-    <t>CAMEL ACT.P MINT 20S</t>
-  </si>
-  <si>
-    <t>20128470</t>
-  </si>
-  <si>
-    <t>CAMEL OPT PURPLE 16S</t>
-  </si>
-  <si>
-    <t>20106190</t>
-  </si>
-  <si>
-    <t>CAMEL OPT PURPLE 12S</t>
-  </si>
-  <si>
-    <t>20114049</t>
-  </si>
-  <si>
-    <t>CAMEL OPT YELLOW 12S</t>
-  </si>
-  <si>
-    <t>20133512</t>
-  </si>
-  <si>
-    <t>CAMEL ACTV MNTHL 20S</t>
-  </si>
-  <si>
-    <t>20138432</t>
-  </si>
-  <si>
-    <t>CAMEL ICE RED 16S</t>
-  </si>
-  <si>
-    <t>20137297</t>
-  </si>
-  <si>
-    <t>CAMEL  KRETEK12'S</t>
-  </si>
-  <si>
-    <t>20142259</t>
-  </si>
-  <si>
-    <t>CAMEL ICE LIME 16S</t>
-  </si>
-  <si>
-    <t>20143273</t>
-  </si>
-  <si>
-    <t>CAMEL KRETK KLSK 10S</t>
-  </si>
-  <si>
-    <t>20143811</t>
-  </si>
-  <si>
-    <t>JUARA INTNS PUCUK12S</t>
-  </si>
-  <si>
-    <t>20143812</t>
-  </si>
-  <si>
-    <t>JUARA INTNS MRKSA12S</t>
-  </si>
-  <si>
-    <t>20143813</t>
-  </si>
-  <si>
-    <t>JUARA INTNS J/JBU12S</t>
-  </si>
-  <si>
-    <t>20130571</t>
-  </si>
-  <si>
-    <t>WIN FILTER CLICK20'S</t>
-  </si>
-  <si>
-    <t>20119629</t>
-  </si>
-  <si>
-    <t>WIN FILTER 20'S</t>
-  </si>
-  <si>
-    <t>20136050</t>
-  </si>
-  <si>
-    <t>WIN KRETEK BERRY 12S</t>
-  </si>
-  <si>
-    <t>20108797</t>
-  </si>
-  <si>
-    <t>WIN BOLD 20'S</t>
-  </si>
-  <si>
-    <t>20135739</t>
-  </si>
-  <si>
-    <t>CLIMAX ICY BKS 20'S</t>
-  </si>
-  <si>
-    <t>20135737</t>
-  </si>
-  <si>
-    <t>CLIMAX MANGO BKS20'S</t>
-  </si>
-  <si>
-    <t>20135736</t>
-  </si>
-  <si>
-    <t>CLIMAX MIX BKS 20'S</t>
-  </si>
-  <si>
-    <t>20112661</t>
-  </si>
-  <si>
-    <t>ESSE PUNCH POP 16'S</t>
-  </si>
-  <si>
-    <t>20070447</t>
-  </si>
-  <si>
-    <t>ESSE BERRY POP 16'S</t>
-  </si>
-  <si>
-    <t>20093678</t>
-  </si>
-  <si>
-    <t>ESSE BLUE CHNGE 20'S</t>
-  </si>
-  <si>
-    <t>20010960</t>
-  </si>
-  <si>
-    <t>ESSE FILTER BLUE 20S</t>
-  </si>
-  <si>
-    <t>20126307</t>
-  </si>
-  <si>
-    <t>ESSE DOUBLE POP 16'S</t>
-  </si>
-  <si>
-    <t>20138128</t>
-  </si>
-  <si>
-    <t>JUARA  APEL 12S</t>
-  </si>
-  <si>
-    <t>20095302</t>
-  </si>
-  <si>
-    <t>JUARA  TEH 12S</t>
-  </si>
-  <si>
-    <t>20139245</t>
-  </si>
-  <si>
-    <t>JUARA KRT  BERRY 12S</t>
-  </si>
-  <si>
-    <t>20130785</t>
-  </si>
-  <si>
-    <t>JUARA  JAMBU12S</t>
-  </si>
-  <si>
-    <t>20141660</t>
-  </si>
-  <si>
-    <t>JUARA KRT PISANG 12S</t>
-  </si>
-  <si>
-    <t>20142217</t>
-  </si>
-  <si>
-    <t>JUARA KLIK GRN GRP12</t>
-  </si>
-  <si>
-    <t>20142218</t>
-  </si>
-  <si>
-    <t>JUARA KLIK BERRY 12S</t>
-  </si>
-  <si>
-    <t>20085760</t>
-  </si>
-  <si>
-    <t>ESSE CHANGE GRP 20'S</t>
-  </si>
-  <si>
-    <t>20112781</t>
-  </si>
-  <si>
-    <t>ESSE CHNG JUICY 16'S</t>
-  </si>
-  <si>
-    <t>20094203</t>
-  </si>
-  <si>
-    <t>ESSE CHNG JUICY 20'S</t>
-  </si>
-  <si>
-    <t>20112785</t>
-  </si>
-  <si>
-    <t>ESSE CHNG APLMNT 16S</t>
-  </si>
-  <si>
-    <t>20055795</t>
-  </si>
-  <si>
-    <t>ESSE CHNG APLMNT 20S</t>
-  </si>
-  <si>
-    <t>20100795</t>
-  </si>
-  <si>
-    <t>ESSE CHNG DOUB 20'S</t>
-  </si>
-  <si>
-    <t>20143095</t>
-  </si>
-  <si>
-    <t>ESSE CHG DBL PINPL20</t>
-  </si>
-  <si>
-    <t>10010077</t>
-  </si>
-  <si>
-    <t>GG SURYA PRO 16'S</t>
-  </si>
-  <si>
-    <t>20054562</t>
-  </si>
-  <si>
-    <t>GG MILD SHIVER 16'S</t>
-  </si>
-  <si>
-    <t>20029731</t>
-  </si>
-  <si>
-    <t>GG SURYA PRO MLD16'S</t>
-  </si>
-  <si>
-    <t>20048021</t>
-  </si>
-  <si>
-    <t>G/G  SGNTURE 12</t>
-  </si>
-  <si>
-    <t>20069791</t>
-  </si>
-  <si>
-    <t>GG SIGNT MILD 16'S</t>
+    <t>20011159</t>
+  </si>
+  <si>
+    <t>COUNTRY KING SIZE 20</t>
+  </si>
+  <si>
+    <t>20024350</t>
+  </si>
+  <si>
+    <t>COUNTRY LIGHT20S BKS</t>
   </si>
   <si>
     <t>10010078</t>
@@ -1412,6 +1454,12 @@
   </si>
   <si>
     <t>GG KRETEK MRH NEW 12</t>
+  </si>
+  <si>
+    <t>20136764</t>
+  </si>
+  <si>
+    <t>GG  INTERNTNL 12S</t>
   </si>
 </sst>
 </file>
@@ -1804,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2285,10 +2333,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2308,7 +2356,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2328,10 +2376,10 @@
         <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2348,10 +2396,10 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2368,7 +2416,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2388,10 +2436,10 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2408,10 +2456,10 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2428,7 +2476,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -2436,10 +2484,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -2448,7 +2496,7 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2456,10 +2504,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -2468,7 +2516,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2476,10 +2524,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -2488,18 +2536,18 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2508,7 +2556,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2516,10 +2564,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2528,18 +2576,18 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2548,7 +2596,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -2556,10 +2604,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2568,58 +2616,58 @@
         <v>12</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2628,18 +2676,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2648,18 +2696,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2668,18 +2716,18 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2688,18 +2736,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2708,7 +2756,7 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -2716,10 +2764,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2728,7 +2776,7 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -2736,10 +2784,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2748,18 +2796,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2768,7 +2816,7 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2776,10 +2824,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2788,18 +2836,18 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2808,18 +2856,18 @@
         <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2828,18 +2876,18 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2848,7 +2896,7 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>9</v>
@@ -2856,10 +2904,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2868,58 +2916,58 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>124</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2928,7 +2976,7 @@
         <v>18</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2936,10 +2984,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2948,18 +2996,18 @@
         <v>18</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2968,7 +3016,7 @@
         <v>18</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2976,10 +3024,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2988,7 +3036,7 @@
         <v>18</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2996,10 +3044,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3008,7 +3056,7 @@
         <v>18</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -3016,10 +3064,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3028,7 +3076,7 @@
         <v>18</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -3036,10 +3084,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3048,18 +3096,18 @@
         <v>18</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -3068,7 +3116,7 @@
         <v>18</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -3076,10 +3124,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -3088,18 +3136,18 @@
         <v>18</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -3108,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3116,10 +3164,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -3128,7 +3176,7 @@
         <v>18</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -3136,10 +3184,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -3148,18 +3196,18 @@
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -3168,58 +3216,58 @@
         <v>18</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3228,7 +3276,7 @@
         <v>21</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -3236,10 +3284,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3248,7 +3296,7 @@
         <v>21</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -3256,10 +3304,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3268,7 +3316,7 @@
         <v>21</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -3276,10 +3324,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3288,7 +3336,7 @@
         <v>21</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -3296,10 +3344,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3308,7 +3356,7 @@
         <v>21</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -3316,10 +3364,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3328,7 +3376,7 @@
         <v>21</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -3336,10 +3384,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3348,7 +3396,7 @@
         <v>21</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -3356,10 +3404,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3368,7 +3416,7 @@
         <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3376,10 +3424,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3388,7 +3436,7 @@
         <v>21</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -3396,10 +3444,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3408,7 +3456,7 @@
         <v>21</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3416,10 +3464,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3428,7 +3476,7 @@
         <v>21</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3436,19 +3484,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3456,19 +3504,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3476,10 +3524,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3488,7 +3536,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3496,10 +3544,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3508,7 +3556,7 @@
         <v>24</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3516,10 +3564,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3528,7 +3576,7 @@
         <v>24</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3536,10 +3584,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3548,7 +3596,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3556,10 +3604,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3568,7 +3616,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3576,10 +3624,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3588,7 +3636,7 @@
         <v>24</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3596,10 +3644,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3608,7 +3656,7 @@
         <v>24</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3616,10 +3664,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3628,7 +3676,7 @@
         <v>24</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3636,10 +3684,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3648,7 +3696,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3656,10 +3704,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3668,7 +3716,7 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3676,10 +3724,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3688,7 +3736,7 @@
         <v>24</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3696,10 +3744,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3708,7 +3756,7 @@
         <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3716,19 +3764,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3736,19 +3784,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3756,10 +3804,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3768,7 +3816,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3776,10 +3824,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3788,7 +3836,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3796,10 +3844,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3808,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3816,10 +3864,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3828,7 +3876,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3836,10 +3884,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3848,18 +3896,18 @@
         <v>27</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3868,7 +3916,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3876,10 +3924,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3888,18 +3936,18 @@
         <v>27</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3908,7 +3956,7 @@
         <v>27</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3916,19 +3964,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3936,19 +3984,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3956,19 +4004,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3976,19 +4024,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3996,10 +4044,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -4008,7 +4056,7 @@
         <v>30</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -4016,10 +4064,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -4028,7 +4076,7 @@
         <v>30</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -4036,10 +4084,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -4048,7 +4096,7 @@
         <v>30</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -4056,10 +4104,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -4068,7 +4116,7 @@
         <v>30</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -4076,10 +4124,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -4088,7 +4136,7 @@
         <v>30</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -4096,10 +4144,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -4108,7 +4156,7 @@
         <v>30</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -4116,10 +4164,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -4128,7 +4176,7 @@
         <v>30</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -4136,10 +4184,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4148,7 +4196,7 @@
         <v>30</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -4156,10 +4204,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4168,7 +4216,7 @@
         <v>30</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4176,10 +4224,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4188,18 +4236,18 @@
         <v>30</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4208,7 +4256,7 @@
         <v>30</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4216,10 +4264,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4228,18 +4276,18 @@
         <v>30</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>261</v>
+        <v>39</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4248,47 +4296,47 @@
         <v>30</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>264</v>
+        <v>42</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4296,50 +4344,50 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>267</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>270</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4356,10 +4404,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4368,7 +4416,7 @@
         <v>33</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4376,10 +4424,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4388,7 +4436,7 @@
         <v>33</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4396,10 +4444,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4408,7 +4456,7 @@
         <v>33</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4416,10 +4464,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4428,7 +4476,7 @@
         <v>33</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4436,10 +4484,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4448,7 +4496,7 @@
         <v>33</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4456,10 +4504,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4468,7 +4516,7 @@
         <v>33</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4476,10 +4524,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4488,18 +4536,18 @@
         <v>33</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4508,7 +4556,7 @@
         <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4516,10 +4564,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4528,7 +4576,7 @@
         <v>33</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4536,10 +4584,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4548,7 +4596,7 @@
         <v>33</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4556,10 +4604,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4568,18 +4616,18 @@
         <v>33</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4588,7 +4636,7 @@
         <v>33</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4596,10 +4644,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4616,10 +4664,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4631,15 +4679,15 @@
         <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4651,15 +4699,15 @@
         <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4668,7 +4716,7 @@
         <v>33</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4676,10 +4724,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4688,7 +4736,7 @@
         <v>33</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4696,10 +4744,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4708,18 +4756,18 @@
         <v>33</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4728,7 +4776,7 @@
         <v>33</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>9</v>
@@ -4736,10 +4784,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4751,15 +4799,15 @@
         <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4771,15 +4819,15 @@
         <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4796,10 +4844,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4811,15 +4859,15 @@
         <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4831,15 +4879,15 @@
         <v>18</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4851,15 +4899,15 @@
         <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4876,10 +4924,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4896,10 +4944,10 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
@@ -4911,15 +4959,15 @@
         <v>18</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4936,10 +4984,10 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
@@ -4951,15 +4999,15 @@
         <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
@@ -4971,15 +5019,15 @@
         <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -4988,7 +5036,7 @@
         <v>33</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>9</v>
@@ -4996,10 +5044,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -5008,18 +5056,18 @@
         <v>33</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
@@ -5028,7 +5076,7 @@
         <v>33</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>9</v>
@@ -5036,10 +5084,10 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
@@ -5048,7 +5096,7 @@
         <v>33</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>9</v>
@@ -5056,10 +5104,10 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
@@ -5071,15 +5119,15 @@
         <v>21</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
@@ -5091,15 +5139,15 @@
         <v>21</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -5111,15 +5159,15 @@
         <v>21</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
@@ -5131,15 +5179,15 @@
         <v>21</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
@@ -5148,7 +5196,7 @@
         <v>33</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5156,19 +5204,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5176,19 +5224,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5196,19 +5244,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5216,19 +5264,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5236,10 +5284,10 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
@@ -5248,7 +5296,7 @@
         <v>36</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5256,10 +5304,10 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
@@ -5268,7 +5316,7 @@
         <v>36</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5276,10 +5324,10 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
@@ -5288,7 +5336,7 @@
         <v>36</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5296,10 +5344,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5308,7 +5356,7 @@
         <v>36</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5316,10 +5364,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5328,7 +5376,7 @@
         <v>36</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5336,10 +5384,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5348,7 +5396,7 @@
         <v>36</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5356,10 +5404,10 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
@@ -5368,18 +5416,18 @@
         <v>36</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
@@ -5388,7 +5436,7 @@
         <v>36</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5396,10 +5444,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5408,18 +5456,18 @@
         <v>36</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5428,7 +5476,7 @@
         <v>36</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5436,39 +5484,39 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5476,39 +5524,39 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5516,10 +5564,10 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
@@ -5528,7 +5576,7 @@
         <v>39</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5536,10 +5584,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
@@ -5548,7 +5596,7 @@
         <v>39</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5556,10 +5604,10 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
@@ -5568,7 +5616,7 @@
         <v>39</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5576,10 +5624,10 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
@@ -5588,7 +5636,7 @@
         <v>39</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5596,10 +5644,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
@@ -5608,7 +5656,7 @@
         <v>39</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5616,10 +5664,10 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
@@ -5628,7 +5676,7 @@
         <v>39</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5636,10 +5684,10 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
@@ -5648,7 +5696,7 @@
         <v>39</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5656,10 +5704,10 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
@@ -5668,7 +5716,7 @@
         <v>39</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5676,10 +5724,10 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
@@ -5688,7 +5736,7 @@
         <v>39</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5696,10 +5744,10 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
@@ -5708,7 +5756,7 @@
         <v>39</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5716,10 +5764,10 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
@@ -5728,7 +5776,7 @@
         <v>39</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5736,19 +5784,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5756,19 +5804,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E198" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>5</v>
@@ -5776,19 +5824,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>5</v>
@@ -5796,19 +5844,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>5</v>
@@ -5816,10 +5864,10 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
@@ -5828,18 +5876,18 @@
         <v>42</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
@@ -5848,18 +5896,18 @@
         <v>42</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
@@ -5868,18 +5916,18 @@
         <v>42</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
@@ -5888,7 +5936,7 @@
         <v>42</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>5</v>
@@ -5896,10 +5944,10 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
@@ -5908,18 +5956,18 @@
         <v>42</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
@@ -5928,18 +5976,18 @@
         <v>42</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
@@ -5948,18 +5996,18 @@
         <v>42</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
@@ -5968,7 +6016,7 @@
         <v>42</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>5</v>
@@ -5976,10 +6024,10 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
@@ -5988,7 +6036,7 @@
         <v>42</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -5996,10 +6044,10 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
@@ -6008,7 +6056,7 @@
         <v>42</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>5</v>
@@ -6016,19 +6064,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -6036,19 +6084,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>5</v>
@@ -6056,19 +6104,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>5</v>
@@ -6076,19 +6124,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>5</v>
@@ -6096,19 +6144,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>5</v>
@@ -6116,19 +6164,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>5</v>
@@ -6136,19 +6184,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>5</v>
@@ -6156,19 +6204,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
@@ -6176,19 +6224,19 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -6196,19 +6244,19 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>5</v>
@@ -6216,19 +6264,19 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>5</v>
@@ -6236,19 +6284,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>5</v>
@@ -6256,21 +6304,201 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B223" s="1" t="s">
+      <c r="B224" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C223" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E223" s="1" t="s">
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E231" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F223" s="1" t="s">
+      <c r="F231" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F232" s="1" t="s">
         <v>5</v>
       </c>
     </row>
